--- a/artfynd/A 40654-2025 artfynd.xlsx
+++ b/artfynd/A 40654-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112538685</v>
+        <v>112538682</v>
       </c>
       <c r="B2" t="n">
-        <v>73915</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6439</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591188</v>
+        <v>591020</v>
       </c>
       <c r="R2" t="n">
-        <v>6972690</v>
+        <v>6972802</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,16 +775,11 @@
         <v>112538687</v>
       </c>
       <c r="B3" t="n">
-        <v>77746</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -820,7 +810,7 @@
         <v>591139</v>
       </c>
       <c r="R3" t="n">
-        <v>6972663</v>
+        <v>6972662</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112538684</v>
+        <v>112538685</v>
       </c>
       <c r="B4" t="n">
-        <v>89679</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6439</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591172</v>
+        <v>591188</v>
       </c>
       <c r="R4" t="n">
-        <v>6972699</v>
+        <v>6972690</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112538686</v>
+        <v>112538683</v>
       </c>
       <c r="B5" t="n">
-        <v>78809</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79413</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6450</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591164</v>
+        <v>591105</v>
       </c>
       <c r="R5" t="n">
-        <v>6972667</v>
+        <v>6972690</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,6 +1060,103 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>112538686</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Krokmyrsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>591164</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6972667</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-10-05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-10-05</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40654-2025 artfynd.xlsx
+++ b/artfynd/A 40654-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538682</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538687</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538685</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538683</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,8 +1182,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538686</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>